--- a/Flujo/Output/Reporte_Ventas_Por_Proyecto.xlsx
+++ b/Flujo/Output/Reporte_Ventas_Por_Proyecto.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
